--- a/pruebas/ejemplos/3.3-Informe-de-Prueba-EJEMPLO.xlsx
+++ b/pruebas/ejemplos/3.3-Informe-de-Prueba-EJEMPLO.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11 suites / 93 tests pasados</t>
+          <t>11 suites / 94 tests pasados</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>6 suites / 28 tests pasados</t>
+          <t>7 suites / 33 tests pasados</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>npm run lint: 0 errores, warnings no bloqueantes</t>
+          <t>npm run lint: 0 errores, 135 warnings no bloqueantes existentes</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6 suites / 31 tests pasados</t>
+          <t>7 suites / 35 tests pasados</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Suites unitarias dedicadas</t>
+          <t>Suites unitarias dedicadas y e2e learning-support</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>077d316 fix: align simulation canvas color token</t>
+          <t>b66290b base dev + cambios locales de contratos</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>fecbfca test: strengthen service coverage review</t>
+          <t>86b4413 base + cambios locales de contratos</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>feature/unit-tests-qa</t>
+          <t>API feature/unit-tests-qa; APP feature/contract-consistency-fixes</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>fecbfca test: strengthen service coverage review</t>
+          <t>86b4413 base + cambios locales de contratos</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>feature/unit-tests-qa</t>
+          <t>API feature/unit-tests-qa; APP feature/contract-consistency-fixes</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>077d316 fix: align simulation canvas color token</t>
+          <t>b66290b base dev + cambios locales de contratos</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">

--- a/pruebas/ejemplos/3.3-Informe-de-Prueba-EJEMPLO.xlsx
+++ b/pruebas/ejemplos/3.3-Informe-de-Prueba-EJEMPLO.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7 suites / 35 tests pasados</t>
+          <t>12 suites / 66 tests pasados</t>
         </is>
       </c>
     </row>

--- a/pruebas/ejemplos/3.3-Informe-de-Prueba-EJEMPLO.xlsx
+++ b/pruebas/ejemplos/3.3-Informe-de-Prueba-EJEMPLO.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen Ejecutivo'!$A$1:$B$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resultados Detallados'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resultados Detallados'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cobertura'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro de Defectos'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidencia Codigo'!$A$1:$D$3</definedName>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -742,12 +742,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>APP typecheck</t>
+          <t>APP E2E Web</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>npm run typecheck</t>
+          <t>npm run test:e2e</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -757,34 +757,56 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>npm run typecheck OK</t>
+          <t>1 suite Playwright / 3 tests pasados</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>APP typecheck</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>npm run typecheck</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PASO</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>npm run typecheck OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>APP lint</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>npm run lint</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>PASO</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PASO</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>npm run lint: 0 errores, warnings no bloqueantes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
